--- a/cases/04_级联透视/配置.xlsx
+++ b/cases/04_级联透视/配置.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,6 @@
           <t>站点ID,频段,场景,城市,区域</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>5G用户数,下行PRB利用率,上行PRB利用率</t>
@@ -548,7 +547,6 @@
           <t>{站点级}</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>频段</t>
@@ -574,7 +572,6 @@
           <t>频段x场景_站点数</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>第二步：站点级数据→频段×场景交叉</t>
@@ -590,7 +587,6 @@
           <t>{站点级}</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>城市</t>
@@ -616,7 +612,6 @@
           <t>城市x频段_用户数</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>第二步：站点级数据→城市×频段用户数</t>
@@ -632,13 +627,11 @@
           <t>{站点级}</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>区域</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>5G用户数_求和,下行PRB利用率_均值</t>
@@ -654,7 +647,6 @@
           <t>区域汇总</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>第二步：站点级数据→区域级汇总</t>
@@ -670,13 +662,11 @@
           <t>{站点级}</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>频段</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>站点ID,5G用户数_求和</t>
@@ -692,10 +682,49 @@
           <t>频段汇总</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>第二步：站点级数据→频段汇总</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>{站点级} JOIN 场景映射表.xlsx ON 场景=场景</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>场景</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>场景类型</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>站点ID</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>场景类型站点数</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>区块与文件JOIN</t>
         </is>
       </c>
     </row>
